--- a/artfynd/S 1559-2025 artfynd.xlsx
+++ b/artfynd/S 1559-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137424656</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137424653</v>
       </c>
       <c r="B3" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1559-2025 artfynd.xlsx
+++ b/artfynd/S 1559-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137424656</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137424653</v>
       </c>
       <c r="B3" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/S 1559-2025 artfynd.xlsx
+++ b/artfynd/S 1559-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137424656</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>137424653</v>
       </c>
       <c r="B3" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
